--- a/BaudRatesForF28379D/baudrates.xlsx
+++ b/BaudRatesForF28379D/baudrates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dan\GitHubs\SE423Spring26\BaudRatesForF28379D\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CBBE910-6AB6-49FC-8F33-3E15A3974D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5C2C90-7743-4C85-BF28-E07A8F81A86B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
   <si>
     <t>clk</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>B3500000</t>
+  </si>
+  <si>
+    <t>But if we change LSPCLK to 200Mhz the slowest bit rate for SPI is 200000000/128 = 1562500 IMU right now is at 1000000 rate, would have to test</t>
   </si>
 </sst>
 </file>
@@ -460,24 +463,27 @@
         <f>(200000000/(16))</f>
         <v>12500000</v>
       </c>
+      <c r="R2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B2:B33" si="0">(50000000/(8*(A3+1)))</f>
+        <f t="shared" ref="B3:B33" si="0">(50000000/(8*(A3+1)))</f>
         <v>3125000</v>
       </c>
       <c r="C3">
         <v>3000000</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D11" si="1">B3/C3</f>
+        <f t="shared" ref="D3:D8" si="1">B3/C3</f>
         <v>1.0416666666666667</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L2:L33" si="2">(100000000/(8*(A3+1)))</f>
+        <f t="shared" ref="L3:L33" si="2">(100000000/(8*(A3+1)))</f>
         <v>6250000</v>
       </c>
       <c r="Q3">
